--- a/Labs/Lab2/Assignment2Rubric.xlsx
+++ b/Labs/Lab2/Assignment2Rubric.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28324"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10916"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Repos\CS246-CourseMaterials\Labs\Lab2\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/birdb/Projects/CS246-CourseMaterials/Labs/Lab2/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{34B7ADFB-08CE-41BA-9457-D276C91F7799}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7D40F15B-A3B2-CC41-98FC-C7DAE64143EF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="38700" yWindow="5790" windowWidth="14985" windowHeight="13050" activeTab="1" xr2:uid="{2ED55EEA-81A7-FF44-BCE3-68AB9ADB8259}"/>
+    <workbookView xWindow="-17760" yWindow="1220" windowWidth="13900" windowHeight="20680" activeTab="1" xr2:uid="{2ED55EEA-81A7-FF44-BCE3-68AB9ADB8259}"/>
   </bookViews>
   <sheets>
     <sheet name="Rubric" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="26">
   <si>
     <t>Requirements</t>
   </si>
@@ -108,14 +108,20 @@
     <t>Team contribution report</t>
   </si>
   <si>
-    <t>Your team did an excellent job on this lab. Your user stories are well written and you did a good job of adding them to epics. You did a good job of setting up the first sprint. There are just a couple issues which are noted below.</t>
+    <t>Yes</t>
+  </si>
+  <si>
+    <t>Good</t>
+  </si>
+  <si>
+    <t>Your team did an excellent job on this lab. Your user stories are well written and you did a good job of adding them to epics. You did a good job of setting up the first sprint.</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="8" x14ac:knownFonts="1">
+  <fonts count="8">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -162,12 +168,14 @@
       <sz val="11"/>
       <color theme="1"/>
       <name val="Helvetica"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="10"/>
       <color theme="1"/>
       <name val="Helvetica"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
@@ -190,7 +198,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -200,19 +208,16 @@
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="49" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -528,32 +533,32 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CFCD13E5-EC24-C14D-9BEE-EA2BBE4DEF6B}">
   <dimension ref="A1:C17"/>
-  <sheetFormatPr defaultColWidth="11.19921875" defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.1640625" defaultRowHeight="16"/>
   <cols>
-    <col min="1" max="1" width="27.796875" customWidth="1"/>
-    <col min="2" max="2" width="9.296875" customWidth="1"/>
+    <col min="1" max="1" width="27.83203125" customWidth="1"/>
+    <col min="2" max="2" width="9.33203125" customWidth="1"/>
     <col min="3" max="3" width="11" customWidth="1"/>
-    <col min="4" max="4" width="10.296875" customWidth="1"/>
+    <col min="4" max="4" width="10.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3">
       <c r="A1" s="1" t="s">
         <v>4</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3">
       <c r="A2" s="3" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3">
       <c r="A3" s="2"/>
       <c r="B3" s="2"/>
       <c r="C3" s="2"/>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:3">
       <c r="A4" s="1" t="s">
         <v>0</v>
       </c>
@@ -562,14 +567,14 @@
       </c>
       <c r="C4" s="2"/>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:3">
       <c r="A5" s="1" t="s">
         <v>8</v>
       </c>
       <c r="B5" s="2"/>
       <c r="C5" s="2"/>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:3">
       <c r="A6" s="4" t="s">
         <v>14</v>
       </c>
@@ -578,8 +583,8 @@
       </c>
       <c r="C6" s="2"/>
     </row>
-    <row r="7" spans="1:3" ht="27" x14ac:dyDescent="0.3">
-      <c r="A7" s="8" t="s">
+    <row r="7" spans="1:3" ht="29">
+      <c r="A7" s="7" t="s">
         <v>18</v>
       </c>
       <c r="B7" s="2">
@@ -587,7 +592,7 @@
       </c>
       <c r="C7" s="2"/>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:3">
       <c r="A8" s="4" t="s">
         <v>11</v>
       </c>
@@ -596,7 +601,7 @@
       </c>
       <c r="C8" s="2"/>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:3">
       <c r="A9" s="4" t="s">
         <v>15</v>
       </c>
@@ -605,7 +610,7 @@
       </c>
       <c r="C9" s="2"/>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:3">
       <c r="A10" s="4" t="s">
         <v>5</v>
       </c>
@@ -614,7 +619,7 @@
       </c>
       <c r="C10" s="2"/>
     </row>
-    <row r="11" spans="1:3" s="5" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:3" s="5" customFormat="1">
       <c r="A11" s="4" t="s">
         <v>12</v>
       </c>
@@ -623,14 +628,14 @@
       </c>
       <c r="C11" s="2"/>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:3">
       <c r="A12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="B12" s="1"/>
       <c r="C12" s="1"/>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:3">
       <c r="A13" s="4" t="s">
         <v>13</v>
       </c>
@@ -639,7 +644,7 @@
       </c>
       <c r="C13" s="2"/>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:3">
       <c r="A14" s="4" t="s">
         <v>6</v>
       </c>
@@ -648,7 +653,7 @@
       </c>
       <c r="C14" s="2"/>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:3">
       <c r="A15" s="4" t="s">
         <v>10</v>
       </c>
@@ -657,7 +662,7 @@
       </c>
       <c r="C15" s="2"/>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:3">
       <c r="A17" s="2" t="s">
         <v>3</v>
       </c>
@@ -675,16 +680,16 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C8EF6DB9-5046-F545-B378-AB8AF91CAAF1}">
   <dimension ref="A1:E23"/>
-  <sheetFormatPr defaultColWidth="11.19921875" defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.1640625" defaultRowHeight="16"/>
   <cols>
-    <col min="1" max="1" width="23.19921875" customWidth="1"/>
-    <col min="2" max="2" width="8.796875" customWidth="1"/>
-    <col min="3" max="3" width="6.796875" customWidth="1"/>
+    <col min="1" max="1" width="23.1640625" customWidth="1"/>
+    <col min="2" max="2" width="8.83203125" customWidth="1"/>
+    <col min="3" max="3" width="6.83203125" customWidth="1"/>
     <col min="4" max="4" width="1.5" customWidth="1"/>
     <col min="5" max="5" width="23.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:5">
       <c r="A1" s="1" t="s">
         <v>4</v>
       </c>
@@ -692,27 +697,27 @@
       <c r="C1" s="2"/>
       <c r="D1" s="2"/>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:5">
       <c r="A2" s="3" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="3" spans="1:5" ht="46.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="10" t="s">
-        <v>23</v>
-      </c>
-      <c r="B3" s="9"/>
-      <c r="C3" s="9"/>
-      <c r="D3" s="9"/>
-      <c r="E3" s="9"/>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:5" ht="46.25" customHeight="1">
+      <c r="A3" s="9" t="s">
+        <v>25</v>
+      </c>
+      <c r="B3" s="10"/>
+      <c r="C3" s="10"/>
+      <c r="D3" s="10"/>
+      <c r="E3" s="10"/>
+    </row>
+    <row r="4" spans="1:5">
       <c r="A4" s="2"/>
       <c r="B4" s="2"/>
       <c r="C4" s="2"/>
       <c r="D4" s="2"/>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:5">
       <c r="A5" s="1" t="s">
         <v>19</v>
       </c>
@@ -725,7 +730,7 @@
       <c r="D5" s="2"/>
       <c r="E5" s="6"/>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:5">
       <c r="A6" s="1" t="s">
         <v>8</v>
       </c>
@@ -734,7 +739,7 @@
       <c r="D6" s="2"/>
       <c r="E6" s="6"/>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:5" ht="17">
       <c r="A7" s="4" t="s">
         <v>14</v>
       </c>
@@ -745,9 +750,11 @@
         <v>20</v>
       </c>
       <c r="D7" s="2"/>
-      <c r="E7" s="6"/>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="E7" s="6" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" ht="17">
       <c r="A8" s="4" t="s">
         <v>17</v>
       </c>
@@ -758,9 +765,11 @@
         <v>15</v>
       </c>
       <c r="D8" s="2"/>
-      <c r="E8" s="6"/>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="E8" s="6" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" ht="17">
       <c r="A9" s="4" t="s">
         <v>11</v>
       </c>
@@ -771,9 +780,11 @@
         <v>8</v>
       </c>
       <c r="D9" s="2"/>
-      <c r="E9" s="6"/>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="E9" s="6" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" ht="17">
       <c r="A10" s="4" t="s">
         <v>15</v>
       </c>
@@ -784,9 +795,11 @@
         <v>4</v>
       </c>
       <c r="D10" s="2"/>
-      <c r="E10" s="6"/>
-    </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="E10" s="6" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" ht="17">
       <c r="A11" s="4" t="s">
         <v>5</v>
       </c>
@@ -797,9 +810,11 @@
         <v>10</v>
       </c>
       <c r="D11" s="2"/>
-      <c r="E11" s="6"/>
-    </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="E11" s="6" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" ht="17">
       <c r="A12" s="4" t="s">
         <v>12</v>
       </c>
@@ -810,16 +825,18 @@
         <v>8</v>
       </c>
       <c r="D12" s="2"/>
-      <c r="E12" s="6"/>
-    </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="E12" s="6" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5">
       <c r="A13" s="4"/>
       <c r="B13" s="2"/>
       <c r="C13" s="2"/>
       <c r="D13" s="2"/>
       <c r="E13" s="6"/>
     </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:5">
       <c r="A14" s="1" t="s">
         <v>7</v>
       </c>
@@ -828,7 +845,7 @@
       <c r="D14" s="2"/>
       <c r="E14" s="6"/>
     </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:5" ht="17">
       <c r="A15" s="4" t="s">
         <v>13</v>
       </c>
@@ -839,9 +856,11 @@
         <v>8</v>
       </c>
       <c r="D15" s="2"/>
-      <c r="E15" s="6"/>
-    </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="E15" s="6" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" ht="17">
       <c r="A16" s="4" t="s">
         <v>6</v>
       </c>
@@ -852,9 +871,11 @@
         <v>4</v>
       </c>
       <c r="D16" s="2"/>
-      <c r="E16" s="6"/>
-    </row>
-    <row r="17" spans="1:5" s="5" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="E16" s="6" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" s="5" customFormat="1" ht="17">
       <c r="A17" s="4" t="s">
         <v>16</v>
       </c>
@@ -865,20 +886,22 @@
         <v>8</v>
       </c>
       <c r="D17" s="1"/>
-      <c r="E17" s="7"/>
-    </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="E17" s="6" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5">
       <c r="D18" s="2"/>
       <c r="E18" s="6"/>
     </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A19" s="11" t="s">
+    <row r="19" spans="1:5">
+      <c r="A19" s="8" t="s">
         <v>20</v>
       </c>
       <c r="D19" s="2"/>
       <c r="E19" s="6"/>
     </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:5" ht="17">
       <c r="A20" s="4" t="s">
         <v>21</v>
       </c>
@@ -889,9 +912,11 @@
         <v>10</v>
       </c>
       <c r="D20" s="2"/>
-      <c r="E20" s="6"/>
-    </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="E20" s="6" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" ht="17">
       <c r="A21" s="4" t="s">
         <v>22</v>
       </c>
@@ -901,13 +926,15 @@
       <c r="C21" s="2">
         <v>5</v>
       </c>
-      <c r="E21" s="6"/>
-    </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="E21" s="6" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5">
       <c r="A22" s="4"/>
       <c r="E22" s="6"/>
     </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:5">
       <c r="A23" s="2" t="s">
         <v>3</v>
       </c>
